--- a/backtest_runs/20260410_193731/by_symbol/CENI/CENI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/CENI/CENI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>104452.66</v>
@@ -817,7 +817,7 @@
         <v>-1688.940000000003</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>102763.72</v>
@@ -909,7 +909,7 @@
         <v>-2780.780000000004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>99982.93999999999</v>
@@ -955,7 +955,7 @@
         <v>-2900.200000000005</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>97082.73999999999</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97082.73999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-2729.59999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>96059.14</v>
@@ -1277,7 +1277,7 @@
         <v>-1245.380000000007</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>96639.17999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-187.659999999999</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>98140.45999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-375.3199999999981</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>98805.79999999999</v>
